--- a/campanas/260413_corazul/corazul_4.xlsx
+++ b/campanas/260413_corazul/corazul_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegopaezmacias/GRIDDED.AGENCY local/00_GRIDDED AGENCY/cdn/campanas/260413_corazul/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7296FB-B088-2340-A2FE-C2849C964C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DE216E-74F7-7B48-8716-0D7FAC007FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23020" yWindow="600" windowWidth="21620" windowHeight="24600" xr2:uid="{2D451190-10EE-ED4B-AA2F-DB570B07E6FB}"/>
+    <workbookView xWindow="9760" yWindow="600" windowWidth="34880" windowHeight="24600" xr2:uid="{2D451190-10EE-ED4B-AA2F-DB570B07E6FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="645">
   <si>
     <t>Jose</t>
   </si>
@@ -265,12 +265,6 @@
     <t>669986191</t>
   </si>
   <si>
-    <t>ESTELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 34 976439878</t>
-  </si>
-  <si>
     <t>ANA ISABEL HERRADOR</t>
   </si>
   <si>
@@ -494,6 +488,1488 @@
   </si>
   <si>
     <t>665098278</t>
+  </si>
+  <si>
+    <t>Marta Asorey Salinas</t>
+  </si>
+  <si>
+    <t>677412193</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>34651133313</t>
+  </si>
+  <si>
+    <t>Kristina Mihranyan</t>
+  </si>
+  <si>
+    <t>638987542</t>
+  </si>
+  <si>
+    <t>CRISTINA</t>
+  </si>
+  <si>
+    <t>651867217</t>
+  </si>
+  <si>
+    <t>Lidia Anguera Cabezuelo</t>
+  </si>
+  <si>
+    <t>650712406</t>
+  </si>
+  <si>
+    <t>juan luis</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 610433674</t>
+  </si>
+  <si>
+    <t>laura</t>
+  </si>
+  <si>
+    <t>667989489</t>
+  </si>
+  <si>
+    <t>659084684</t>
+  </si>
+  <si>
+    <t>ONOFRE Simón</t>
+  </si>
+  <si>
+    <t>0034695930758</t>
+  </si>
+  <si>
+    <t>Noemi Bonache GIl</t>
+  </si>
+  <si>
+    <t>697793080</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>610729398</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>+345552112121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irina </t>
+  </si>
+  <si>
+    <t>691172951</t>
+  </si>
+  <si>
+    <t>Montserrat Castro Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 696306917</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>691172953</t>
+  </si>
+  <si>
+    <t>Nuria</t>
+  </si>
+  <si>
+    <t>630508685</t>
+  </si>
+  <si>
+    <t>Mónica Piccoli</t>
+  </si>
+  <si>
+    <t>629981696</t>
+  </si>
+  <si>
+    <t>0034625789130</t>
+  </si>
+  <si>
+    <t>Alberto Álvarez Martínez</t>
+  </si>
+  <si>
+    <t>625976559</t>
+  </si>
+  <si>
+    <t>Laura, Rodriguez Turia</t>
+  </si>
+  <si>
+    <t>633887957</t>
+  </si>
+  <si>
+    <t>Francisco j raurich</t>
+  </si>
+  <si>
+    <t>609974262</t>
+  </si>
+  <si>
+    <t>María Teresa</t>
+  </si>
+  <si>
+    <t>605455150</t>
+  </si>
+  <si>
+    <t>Maria Jose</t>
+  </si>
+  <si>
+    <t>657466422</t>
+  </si>
+  <si>
+    <t>María López Abril</t>
+  </si>
+  <si>
+    <t>626570763</t>
+  </si>
+  <si>
+    <t>SILVIA MORENO SANCHEZ</t>
+  </si>
+  <si>
+    <t>María José</t>
+  </si>
+  <si>
+    <t>654753838</t>
+  </si>
+  <si>
+    <t>Puri Miralles</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 685452503</t>
+  </si>
+  <si>
+    <t>Oscar elvira rodriguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 600256551</t>
+  </si>
+  <si>
+    <t>Victoria Macia Garay</t>
+  </si>
+  <si>
+    <t>654534672</t>
+  </si>
+  <si>
+    <t>Soraya garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 676037499</t>
+  </si>
+  <si>
+    <t>María Ángeles Quintero</t>
+  </si>
+  <si>
+    <t>686888352</t>
+  </si>
+  <si>
+    <t>Deta</t>
+  </si>
+  <si>
+    <t>660764548</t>
+  </si>
+  <si>
+    <t>Jose Larios Cerezo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 609187732</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>655604996</t>
+  </si>
+  <si>
+    <t>CRIS</t>
+  </si>
+  <si>
+    <t>699340608</t>
+  </si>
+  <si>
+    <t>CINDY</t>
+  </si>
+  <si>
+    <t>687094415</t>
+  </si>
+  <si>
+    <t>lourdes</t>
+  </si>
+  <si>
+    <t>653226787</t>
+  </si>
+  <si>
+    <t>María Victoria López</t>
+  </si>
+  <si>
+    <t>627782375</t>
+  </si>
+  <si>
+    <t>Noelia</t>
+  </si>
+  <si>
+    <t>633684016</t>
+  </si>
+  <si>
+    <t>Sandra Soriano</t>
+  </si>
+  <si>
+    <t>600586060</t>
+  </si>
+  <si>
+    <t>Alvaro</t>
+  </si>
+  <si>
+    <t>665470007</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>610004151</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>+34662298395</t>
+  </si>
+  <si>
+    <t>JOSEP MARIA ROIGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 637987985</t>
+  </si>
+  <si>
+    <t>Bego Boedo</t>
+  </si>
+  <si>
+    <t>629566143</t>
+  </si>
+  <si>
+    <t>Janet Mascia Pozo</t>
+  </si>
+  <si>
+    <t>652844528</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>692026291</t>
+  </si>
+  <si>
+    <t>Juan Andrés</t>
+  </si>
+  <si>
+    <t>0034607391717</t>
+  </si>
+  <si>
+    <t>Inma</t>
+  </si>
+  <si>
+    <t>0034600505356</t>
+  </si>
+  <si>
+    <t>GEMA</t>
+  </si>
+  <si>
+    <t>677678420</t>
+  </si>
+  <si>
+    <t>IBAN</t>
+  </si>
+  <si>
+    <t>609002653</t>
+  </si>
+  <si>
+    <t>kalifa</t>
+  </si>
+  <si>
+    <t>671107432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAN LOZANO </t>
+  </si>
+  <si>
+    <t>620917609</t>
+  </si>
+  <si>
+    <t>Laura HERNANDEZ MORALES</t>
+  </si>
+  <si>
+    <t>605958286</t>
+  </si>
+  <si>
+    <t>Alberto Zambrana Marti</t>
+  </si>
+  <si>
+    <t>+34603297881</t>
+  </si>
+  <si>
+    <t>MARI MAR MORALES LAZARO</t>
+  </si>
+  <si>
+    <t>625051390</t>
+  </si>
+  <si>
+    <t>Raquel Tomás Martínez</t>
+  </si>
+  <si>
+    <t>626832368</t>
+  </si>
+  <si>
+    <t>MARIA DEL MAR</t>
+  </si>
+  <si>
+    <t>0034625051390</t>
+  </si>
+  <si>
+    <t>Stephanie Cliffodd</t>
+  </si>
+  <si>
+    <t>673167760</t>
+  </si>
+  <si>
+    <t>Sara Alcántara Tamayo</t>
+  </si>
+  <si>
+    <t>617023321</t>
+  </si>
+  <si>
+    <t>Carmen Jarque</t>
+  </si>
+  <si>
+    <t>678741878</t>
+  </si>
+  <si>
+    <t>Francisco Rodriguez Jiménez</t>
+  </si>
+  <si>
+    <t>676802886</t>
+  </si>
+  <si>
+    <t>Aly</t>
+  </si>
+  <si>
+    <t>676423577</t>
+  </si>
+  <si>
+    <t>Miriam López albiol</t>
+  </si>
+  <si>
+    <t>664351472</t>
+  </si>
+  <si>
+    <t>Almudena Rico Tejero</t>
+  </si>
+  <si>
+    <t>687637914</t>
+  </si>
+  <si>
+    <t>Vanessa Pérez Andrada</t>
+  </si>
+  <si>
+    <t>651184281</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>636838301</t>
+  </si>
+  <si>
+    <t>Leticia Molano</t>
+  </si>
+  <si>
+    <t>34630312251</t>
+  </si>
+  <si>
+    <t>Sofía selma</t>
+  </si>
+  <si>
+    <t>687378990</t>
+  </si>
+  <si>
+    <t>Lucia</t>
+  </si>
+  <si>
+    <t>651945690</t>
+  </si>
+  <si>
+    <t>Ana Maria</t>
+  </si>
+  <si>
+    <t>657467759</t>
+  </si>
+  <si>
+    <t>DESIREE PRIETO SANCHEZ</t>
+  </si>
+  <si>
+    <t>661334636</t>
+  </si>
+  <si>
+    <t>diana valencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 697519913</t>
+  </si>
+  <si>
+    <t>María Fuentes</t>
+  </si>
+  <si>
+    <t>662283313</t>
+  </si>
+  <si>
+    <t>Ana redondo santana</t>
+  </si>
+  <si>
+    <t>661110871</t>
+  </si>
+  <si>
+    <t>Maria del Carmen de Haro</t>
+  </si>
+  <si>
+    <t>636397867</t>
+  </si>
+  <si>
+    <t>34 663857282</t>
+  </si>
+  <si>
+    <t>Jonas</t>
+  </si>
+  <si>
+    <t>651839082</t>
+  </si>
+  <si>
+    <t>Victoria pons</t>
+  </si>
+  <si>
+    <t>606452752</t>
+  </si>
+  <si>
+    <t>Sandra Casadevall</t>
+  </si>
+  <si>
+    <t>609306798</t>
+  </si>
+  <si>
+    <t>Elisabet Arazola Carrasquilla</t>
+  </si>
+  <si>
+    <t>687806313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azadeh </t>
+  </si>
+  <si>
+    <t>660083510</t>
+  </si>
+  <si>
+    <t>Ismael Fernandez</t>
+  </si>
+  <si>
+    <t>603646956</t>
+  </si>
+  <si>
+    <t>Estela</t>
+  </si>
+  <si>
+    <t>605344258</t>
+  </si>
+  <si>
+    <t>Emilio Javier Sola</t>
+  </si>
+  <si>
+    <t>609062960</t>
+  </si>
+  <si>
+    <t>Noemí Manubens</t>
+  </si>
+  <si>
+    <t>630621926</t>
+  </si>
+  <si>
+    <t>Pablo Hernández vaño</t>
+  </si>
+  <si>
+    <t>650000643</t>
+  </si>
+  <si>
+    <t>Agustin Rodríguez</t>
+  </si>
+  <si>
+    <t>633202951</t>
+  </si>
+  <si>
+    <t>Natalia Briceño Justo</t>
+  </si>
+  <si>
+    <t>616077786</t>
+  </si>
+  <si>
+    <t>Alba Rodriguez</t>
+  </si>
+  <si>
+    <t>620687158</t>
+  </si>
+  <si>
+    <t>Gracia</t>
+  </si>
+  <si>
+    <t>34666029340</t>
+  </si>
+  <si>
+    <t>Sonia Vargas López</t>
+  </si>
+  <si>
+    <t>678227300</t>
+  </si>
+  <si>
+    <t>Ana Cubero Galarregui</t>
+  </si>
+  <si>
+    <t>629503812</t>
+  </si>
+  <si>
+    <t>Rocio</t>
+  </si>
+  <si>
+    <t>684236090</t>
+  </si>
+  <si>
+    <t>elisabet</t>
+  </si>
+  <si>
+    <t>618041026</t>
+  </si>
+  <si>
+    <t>Sandra Moreira Perez</t>
+  </si>
+  <si>
+    <t>616533020</t>
+  </si>
+  <si>
+    <t>AFRICA</t>
+  </si>
+  <si>
+    <t>645251045</t>
+  </si>
+  <si>
+    <t>Amparo</t>
+  </si>
+  <si>
+    <t>34622893321</t>
+  </si>
+  <si>
+    <t>Mónica</t>
+  </si>
+  <si>
+    <t>0034644871469</t>
+  </si>
+  <si>
+    <t>Wendy isabel Marichal Martin</t>
+  </si>
+  <si>
+    <t>644829829</t>
+  </si>
+  <si>
+    <t>MARIA VICTORIA SEDA SANCHEZ</t>
+  </si>
+  <si>
+    <t>655857485</t>
+  </si>
+  <si>
+    <t>Ángel Sánchez</t>
+  </si>
+  <si>
+    <t>625355500</t>
+  </si>
+  <si>
+    <t>mari carmen</t>
+  </si>
+  <si>
+    <t>34655133069</t>
+  </si>
+  <si>
+    <t>TERESA</t>
+  </si>
+  <si>
+    <t>658638795</t>
+  </si>
+  <si>
+    <t>Marisa</t>
+  </si>
+  <si>
+    <t>0034657845423</t>
+  </si>
+  <si>
+    <t>Carmen Rojas García</t>
+  </si>
+  <si>
+    <t>692774664</t>
+  </si>
+  <si>
+    <t>Noemi</t>
+  </si>
+  <si>
+    <t>634303133</t>
+  </si>
+  <si>
+    <t>judit tomas aznar</t>
+  </si>
+  <si>
+    <t>638185416</t>
+  </si>
+  <si>
+    <t>Laura Olivas</t>
+  </si>
+  <si>
+    <t>605078508</t>
+  </si>
+  <si>
+    <t>cristina fuentes torres</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 625213057</t>
+  </si>
+  <si>
+    <t>Pepa</t>
+  </si>
+  <si>
+    <t>655840480</t>
+  </si>
+  <si>
+    <t>Yolanda Moya</t>
+  </si>
+  <si>
+    <t>681212742</t>
+  </si>
+  <si>
+    <t>Juan Manuel Cespedes Robles</t>
+  </si>
+  <si>
+    <t>640732177</t>
+  </si>
+  <si>
+    <t>Rosa  M Martínez</t>
+  </si>
+  <si>
+    <t>34625421569</t>
+  </si>
+  <si>
+    <t>Miriam</t>
+  </si>
+  <si>
+    <t>34637958586</t>
+  </si>
+  <si>
+    <t>RODRIGO</t>
+  </si>
+  <si>
+    <t>660062290</t>
+  </si>
+  <si>
+    <t>Montse</t>
+  </si>
+  <si>
+    <t>622749391</t>
+  </si>
+  <si>
+    <t>Javier Guillamon</t>
+  </si>
+  <si>
+    <t>666978596</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Núñez</t>
+  </si>
+  <si>
+    <t>625617218</t>
+  </si>
+  <si>
+    <t>657412048</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>0034607621500</t>
+  </si>
+  <si>
+    <t>MARIA JESUS VINDEL IBAÑEZ</t>
+  </si>
+  <si>
+    <t>676358150</t>
+  </si>
+  <si>
+    <t>Joel López Galán</t>
+  </si>
+  <si>
+    <t>698950791</t>
+  </si>
+  <si>
+    <t>Miriam González Blanes</t>
+  </si>
+  <si>
+    <t>679018124</t>
+  </si>
+  <si>
+    <t>0034663710609</t>
+  </si>
+  <si>
+    <t>MARIA JOSEFA EGEA CARRILLO</t>
+  </si>
+  <si>
+    <t>619725355</t>
+  </si>
+  <si>
+    <t>Oriol Domènech Farré</t>
+  </si>
+  <si>
+    <t>622908050</t>
+  </si>
+  <si>
+    <t>Laura (isaac)</t>
+  </si>
+  <si>
+    <t>677860359</t>
+  </si>
+  <si>
+    <t>Raquel</t>
+  </si>
+  <si>
+    <t>665885401</t>
+  </si>
+  <si>
+    <t>Estefania Mateo Rojano</t>
+  </si>
+  <si>
+    <t>643078037</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>677149633</t>
+  </si>
+  <si>
+    <t>Irina Camelia</t>
+  </si>
+  <si>
+    <t>662251297</t>
+  </si>
+  <si>
+    <t>MARTA</t>
+  </si>
+  <si>
+    <t>615967764</t>
+  </si>
+  <si>
+    <t>Antía</t>
+  </si>
+  <si>
+    <t>627976317</t>
+  </si>
+  <si>
+    <t>692716619</t>
+  </si>
+  <si>
+    <t>Esther Tomas</t>
+  </si>
+  <si>
+    <t>657303073</t>
+  </si>
+  <si>
+    <t>Lucia Martin</t>
+  </si>
+  <si>
+    <t>622177154</t>
+  </si>
+  <si>
+    <t>Raquel López Pérez</t>
+  </si>
+  <si>
+    <t>661811752</t>
+  </si>
+  <si>
+    <t>virginia</t>
+  </si>
+  <si>
+    <t>34699348088</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>646811727</t>
+  </si>
+  <si>
+    <t>Maria del Mar Sanchez Reina</t>
+  </si>
+  <si>
+    <t>608959129</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>606374334</t>
+  </si>
+  <si>
+    <t>Ana lacoume</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 670658906</t>
+  </si>
+  <si>
+    <t>jenifer perez hernandez</t>
+  </si>
+  <si>
+    <t>680979287</t>
+  </si>
+  <si>
+    <t>Irene Pacheco</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 617025312</t>
+  </si>
+  <si>
+    <t>Paula Dios</t>
+  </si>
+  <si>
+    <t>658896467</t>
+  </si>
+  <si>
+    <t>Juan caro</t>
+  </si>
+  <si>
+    <t>655704136</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>679989100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatriz </t>
+  </si>
+  <si>
+    <t>34692837727</t>
+  </si>
+  <si>
+    <t>Manuel Cubero algar</t>
+  </si>
+  <si>
+    <t>670997520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruben </t>
+  </si>
+  <si>
+    <t>627540576</t>
+  </si>
+  <si>
+    <t>christian López</t>
+  </si>
+  <si>
+    <t>678611996</t>
+  </si>
+  <si>
+    <t>Encarni Sereno</t>
+  </si>
+  <si>
+    <t>630338430</t>
+  </si>
+  <si>
+    <t>MARIA LAURA</t>
+  </si>
+  <si>
+    <t>663323550</t>
+  </si>
+  <si>
+    <t>Nuria silla tejero</t>
+  </si>
+  <si>
+    <t>633783017</t>
+  </si>
+  <si>
+    <t>Raúl Martín Virues</t>
+  </si>
+  <si>
+    <t>722193990</t>
+  </si>
+  <si>
+    <t>paula pérez</t>
+  </si>
+  <si>
+    <t>641217360</t>
+  </si>
+  <si>
+    <t>Asunción Ferrando Brines</t>
+  </si>
+  <si>
+    <t>696843690</t>
+  </si>
+  <si>
+    <t>María Fernandez Cagigas</t>
+  </si>
+  <si>
+    <t>608787095</t>
+  </si>
+  <si>
+    <t>ALEJANDRO ACEBEDO GARCIA</t>
+  </si>
+  <si>
+    <t>661327014</t>
+  </si>
+  <si>
+    <t>Paula Ciges</t>
+  </si>
+  <si>
+    <t>620699966</t>
+  </si>
+  <si>
+    <t>658195481</t>
+  </si>
+  <si>
+    <t>David Blázquez Jiménez</t>
+  </si>
+  <si>
+    <t>686089257</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>625795775</t>
+  </si>
+  <si>
+    <t>ESTHER</t>
+  </si>
+  <si>
+    <t>690339185</t>
+  </si>
+  <si>
+    <t>Francisco Jose García campoy</t>
+  </si>
+  <si>
+    <t>633081219</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>625421569</t>
+  </si>
+  <si>
+    <t>Maria Cano</t>
+  </si>
+  <si>
+    <t>659720345</t>
+  </si>
+  <si>
+    <t>Tania Duran</t>
+  </si>
+  <si>
+    <t>630048411</t>
+  </si>
+  <si>
+    <t>José Antonio</t>
+  </si>
+  <si>
+    <t>655914705</t>
+  </si>
+  <si>
+    <t>Xiana Souto Barreiro</t>
+  </si>
+  <si>
+    <t>682659717</t>
+  </si>
+  <si>
+    <t>Marisa Belmar Muñoz</t>
+  </si>
+  <si>
+    <t>648765095</t>
+  </si>
+  <si>
+    <t>Alicia Seda</t>
+  </si>
+  <si>
+    <t>627679343</t>
+  </si>
+  <si>
+    <t>Teresa Fabres</t>
+  </si>
+  <si>
+    <t>676098634</t>
+  </si>
+  <si>
+    <t>Eva Marrero</t>
+  </si>
+  <si>
+    <t>34684085068</t>
+  </si>
+  <si>
+    <t>Inmaculada sotelo</t>
+  </si>
+  <si>
+    <t>34669593707</t>
+  </si>
+  <si>
+    <t>Yurena</t>
+  </si>
+  <si>
+    <t>626493486</t>
+  </si>
+  <si>
+    <t>Connie Neira</t>
+  </si>
+  <si>
+    <t>692253449</t>
+  </si>
+  <si>
+    <t>SANDRA</t>
+  </si>
+  <si>
+    <t>679778284</t>
+  </si>
+  <si>
+    <t>Raúl García Rodríguez</t>
+  </si>
+  <si>
+    <t>+34613543180</t>
+  </si>
+  <si>
+    <t>Ana Rot</t>
+  </si>
+  <si>
+    <t>670884934</t>
+  </si>
+  <si>
+    <t>Mercedes Garcia Cano</t>
+  </si>
+  <si>
+    <t>684399231</t>
+  </si>
+  <si>
+    <t>Veronica Reig porta</t>
+  </si>
+  <si>
+    <t>691536614</t>
+  </si>
+  <si>
+    <t>Ana Cristina Moreno Calderin</t>
+  </si>
+  <si>
+    <t>603562979</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>617037075</t>
+  </si>
+  <si>
+    <t>Mari Carmen Domenech</t>
+  </si>
+  <si>
+    <t>655902739</t>
+  </si>
+  <si>
+    <t>Mónica Puga Cañoto</t>
+  </si>
+  <si>
+    <t>636747323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yobeiba torres </t>
+  </si>
+  <si>
+    <t>34601085074</t>
+  </si>
+  <si>
+    <t>Susana Schröder</t>
+  </si>
+  <si>
+    <t>696619118</t>
+  </si>
+  <si>
+    <t>Raul hidalgo</t>
+  </si>
+  <si>
+    <t>637375435</t>
+  </si>
+  <si>
+    <t>Pedro Costas</t>
+  </si>
+  <si>
+    <t>670594633</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>651838237</t>
+  </si>
+  <si>
+    <t>Rosario García Torralba</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 654538336</t>
+  </si>
+  <si>
+    <t>Victor rod lan</t>
+  </si>
+  <si>
+    <t>651891718</t>
+  </si>
+  <si>
+    <t>Daniel Muñoz Illana</t>
+  </si>
+  <si>
+    <t>686321149</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>+34605663740</t>
+  </si>
+  <si>
+    <t>sara santiago sosa</t>
+  </si>
+  <si>
+    <t>686063102</t>
+  </si>
+  <si>
+    <t>LAURA RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>652688806</t>
+  </si>
+  <si>
+    <t>Andreina Fernández Jaimes</t>
+  </si>
+  <si>
+    <t>659016103</t>
+  </si>
+  <si>
+    <t>0034669040246</t>
+  </si>
+  <si>
+    <t>Raquel Ortiz Gimenez</t>
+  </si>
+  <si>
+    <t>616881004</t>
+  </si>
+  <si>
+    <t>jenifer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 678251820</t>
+  </si>
+  <si>
+    <t>Silvia Monzonis</t>
+  </si>
+  <si>
+    <t>636622115</t>
+  </si>
+  <si>
+    <t>Sergi Garcia</t>
+  </si>
+  <si>
+    <t>666666665</t>
+  </si>
+  <si>
+    <t>ASUN</t>
+  </si>
+  <si>
+    <t>617984086</t>
+  </si>
+  <si>
+    <t>Ana Benavides</t>
+  </si>
+  <si>
+    <t>34607907154</t>
+  </si>
+  <si>
+    <t>626820547</t>
+  </si>
+  <si>
+    <t>Victoria Palazon villa</t>
+  </si>
+  <si>
+    <t>627206220</t>
+  </si>
+  <si>
+    <t>Miguel Muñoz Collado</t>
+  </si>
+  <si>
+    <t>607793535</t>
+  </si>
+  <si>
+    <t>Alejandro Díaz Molina</t>
+  </si>
+  <si>
+    <t>600094752</t>
+  </si>
+  <si>
+    <t>Vicente Gómez</t>
+  </si>
+  <si>
+    <t>609274789</t>
+  </si>
+  <si>
+    <t>marc heras</t>
+  </si>
+  <si>
+    <t>681036397</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>0034676239249</t>
+  </si>
+  <si>
+    <t>Delia Gómez Santos</t>
+  </si>
+  <si>
+    <t>676034690</t>
+  </si>
+  <si>
+    <t>Jennifer Borja borja</t>
+  </si>
+  <si>
+    <t>634408451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magda Torrecillas </t>
+  </si>
+  <si>
+    <t>669638227</t>
+  </si>
+  <si>
+    <t>LAURA GONZALO</t>
+  </si>
+  <si>
+    <t>647291262</t>
+  </si>
+  <si>
+    <t>ROSI Alemán Ortiz</t>
+  </si>
+  <si>
+    <t>699229967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aroa </t>
+  </si>
+  <si>
+    <t>676773140</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>636982217</t>
+  </si>
+  <si>
+    <t>Pascual Mas</t>
+  </si>
+  <si>
+    <t>622550438</t>
+  </si>
+  <si>
+    <t>680511203</t>
+  </si>
+  <si>
+    <t>Judit Marti Lora</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34 691695597</t>
+  </si>
+  <si>
+    <t>Manuel lachica</t>
+  </si>
+  <si>
+    <t>639229183</t>
+  </si>
+  <si>
+    <t>Laura Díez García</t>
+  </si>
+  <si>
+    <t>630047597</t>
+  </si>
+  <si>
+    <t>Rosario Santamarina</t>
+  </si>
+  <si>
+    <t>609229166</t>
+  </si>
+  <si>
+    <t>Francisco Sanchez García</t>
+  </si>
+  <si>
+    <t>626701109</t>
+  </si>
+  <si>
+    <t>Ariel Ruben</t>
+  </si>
+  <si>
+    <t>680602811</t>
+  </si>
+  <si>
+    <t>Juan Carlos López Garcia</t>
+  </si>
+  <si>
+    <t>639724938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jessica </t>
+  </si>
+  <si>
+    <t>675844752</t>
+  </si>
+  <si>
+    <t>686738196</t>
+  </si>
+  <si>
+    <t>JULIO ALBERTO</t>
+  </si>
+  <si>
+    <t>617751994</t>
+  </si>
+  <si>
+    <t>685887827</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>669223311</t>
+  </si>
+  <si>
+    <t>REYNA</t>
+  </si>
+  <si>
+    <t>679778808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fátima Torres París </t>
+  </si>
+  <si>
+    <t>678145093</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>691305839</t>
+  </si>
+  <si>
+    <t>Andrei</t>
+  </si>
+  <si>
+    <t>34642491463</t>
+  </si>
+  <si>
+    <t>Eli</t>
+  </si>
+  <si>
+    <t>618323772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandra </t>
+  </si>
+  <si>
+    <t>675833860</t>
+  </si>
+  <si>
+    <t>Celia Martínez Vázquez</t>
+  </si>
+  <si>
+    <t>679473296</t>
+  </si>
+  <si>
+    <t>carmen Sanchez</t>
+  </si>
+  <si>
+    <t>678884959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis </t>
+  </si>
+  <si>
+    <t>646427852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">642682967 </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>659222943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verónica </t>
+  </si>
+  <si>
+    <t>667219538</t>
+  </si>
+  <si>
+    <t>Eva María calin</t>
+  </si>
+  <si>
+    <t>669172334</t>
+  </si>
+  <si>
+    <t>Diana Lourido Beiro</t>
+  </si>
+  <si>
+    <t>675956137</t>
+  </si>
+  <si>
+    <t>rocio</t>
+  </si>
+  <si>
+    <t>0034622431435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Jesus </t>
+  </si>
+  <si>
+    <t>Francisco Javier Ramírez Yébenes</t>
+  </si>
+  <si>
+    <t>606831047</t>
+  </si>
+  <si>
+    <t>Alicia Alamos</t>
+  </si>
+  <si>
+    <t>660523455</t>
+  </si>
+  <si>
+    <t>Emi Farré Farran</t>
+  </si>
+  <si>
+    <t>669516077</t>
+  </si>
+  <si>
+    <t>Gabriel Alba navarrete</t>
+  </si>
+  <si>
+    <t>660653558</t>
   </si>
 </sst>
 </file>
@@ -722,8 +2198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F70661F-464D-3E4F-BFB6-59B7B76FAEEC}" name="Tabla2" displayName="Tabla2" ref="C1:F77" totalsRowShown="0" tableBorderDxfId="4">
-  <autoFilter ref="C1:F77" xr:uid="{8F70661F-464D-3E4F-BFB6-59B7B76FAEEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F70661F-464D-3E4F-BFB6-59B7B76FAEEC}" name="Tabla2" displayName="Tabla2" ref="C1:F331" totalsRowShown="0" tableBorderDxfId="4">
+  <autoFilter ref="C1:F331" xr:uid="{8F70661F-464D-3E4F-BFB6-59B7B76FAEEC}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{96022F23-3FEE-5046-A73A-6FD521481172}" name="nombreCliente" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{239BBB18-A2EB-FC46-84AF-56FC396ADC7A}" name="cli_telefono" dataDxfId="2"/>
@@ -1031,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BFDCDFC-0A8F-CF40-9370-BA60E8D4D64F}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F331"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.1640625" style="7" customWidth="1"/>
@@ -1272,10 +2748,10 @@
         <v>77</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -1432,10 +2908,10 @@
         <v>93</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -1452,10 +2928,10 @@
         <v>95</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1472,10 +2948,10 @@
         <v>97</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1492,10 +2968,10 @@
         <v>99</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1612,10 +3088,10 @@
         <v>111</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1632,10 +3108,10 @@
         <v>113</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1692,10 +3168,10 @@
         <v>119</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1732,10 +3208,10 @@
         <v>123</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1808,14 +3284,14 @@
       <c r="C39" t="s">
         <v>130</v>
       </c>
-      <c r="D39" t="s">
-        <v>131</v>
+      <c r="D39">
+        <v>647736520</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1826,16 +3302,16 @@
         <v>46140</v>
       </c>
       <c r="C40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" t="s">
         <v>132</v>
       </c>
-      <c r="D40">
-        <v>647736520</v>
-      </c>
       <c r="E40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -1846,16 +3322,16 @@
         <v>46140</v>
       </c>
       <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" t="s">
         <v>133</v>
       </c>
-      <c r="D41" t="s">
-        <v>134</v>
-      </c>
       <c r="E41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -1866,7 +3342,7 @@
         <v>46140</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
         <v>135</v>
@@ -1886,10 +3362,10 @@
         <v>46140</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -1903,18 +3379,18 @@
         <v>4</v>
       </c>
       <c r="B44" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E44" s="2">
-        <v>2</v>
-      </c>
-      <c r="F44" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C44" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" t="s">
+        <v>154</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44">
         <v>2</v>
       </c>
     </row>
@@ -1923,18 +3399,18 @@
         <v>4</v>
       </c>
       <c r="B45" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2</v>
-      </c>
-      <c r="F45" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C45" t="s">
+        <v>155</v>
+      </c>
+      <c r="D45" t="s">
+        <v>156</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45">
         <v>2</v>
       </c>
     </row>
@@ -1943,18 +3419,18 @@
         <v>4</v>
       </c>
       <c r="B46" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E46" s="2">
-        <v>2</v>
-      </c>
-      <c r="F46" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C46" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
         <v>2</v>
       </c>
     </row>
@@ -1963,16 +3439,18 @@
         <v>4</v>
       </c>
       <c r="B47" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" s="2">
-        <v>2</v>
-      </c>
-      <c r="F47" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C47" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" t="s">
+        <v>160</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47">
         <v>2</v>
       </c>
     </row>
@@ -1981,19 +3459,19 @@
         <v>4</v>
       </c>
       <c r="B48" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E48" s="2">
-        <v>2</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2</v>
+        <v>46140</v>
+      </c>
+      <c r="C48" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" t="s">
+        <v>162</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -2001,18 +3479,18 @@
         <v>4</v>
       </c>
       <c r="B49" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E49" s="2">
-        <v>2</v>
-      </c>
-      <c r="F49" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C49" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" t="s">
+        <v>164</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49">
         <v>2</v>
       </c>
     </row>
@@ -2021,18 +3499,18 @@
         <v>4</v>
       </c>
       <c r="B50" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E50" s="2">
-        <v>2</v>
-      </c>
-      <c r="F50" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C50" t="s">
+        <v>157</v>
+      </c>
+      <c r="D50" t="s">
+        <v>165</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50">
         <v>2</v>
       </c>
     </row>
@@ -2041,18 +3519,18 @@
         <v>4</v>
       </c>
       <c r="B51" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E51" s="2">
-        <v>2</v>
-      </c>
-      <c r="F51" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C51" t="s">
+        <v>166</v>
+      </c>
+      <c r="D51" t="s">
+        <v>167</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51">
         <v>2</v>
       </c>
     </row>
@@ -2061,16 +3539,18 @@
         <v>4</v>
       </c>
       <c r="B52" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" s="2">
-        <v>2</v>
-      </c>
-      <c r="F52" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C52" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" t="s">
+        <v>169</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
         <v>2</v>
       </c>
     </row>
@@ -2079,19 +3559,19 @@
         <v>4</v>
       </c>
       <c r="B53" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="2">
-        <v>4</v>
-      </c>
-      <c r="F53" s="3">
-        <v>0</v>
+        <v>46140</v>
+      </c>
+      <c r="C53" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
@@ -2099,19 +3579,19 @@
         <v>4</v>
       </c>
       <c r="B54" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2">
-        <v>2</v>
-      </c>
-      <c r="F54" s="3">
-        <v>2</v>
+        <v>46140</v>
+      </c>
+      <c r="C54" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
@@ -2119,18 +3599,18 @@
         <v>4</v>
       </c>
       <c r="B55" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="2">
-        <v>2</v>
-      </c>
-      <c r="F55" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C55" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" t="s">
+        <v>175</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55">
         <v>2</v>
       </c>
     </row>
@@ -2139,19 +3619,19 @@
         <v>4</v>
       </c>
       <c r="B56" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="2">
-        <v>4</v>
-      </c>
-      <c r="F56" s="3">
-        <v>0</v>
+        <v>46140</v>
+      </c>
+      <c r="C56" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
@@ -2159,18 +3639,18 @@
         <v>4</v>
       </c>
       <c r="B57" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="2">
-        <v>2</v>
-      </c>
-      <c r="F57" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C57" t="s">
+        <v>178</v>
+      </c>
+      <c r="D57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57">
         <v>2</v>
       </c>
     </row>
@@ -2179,19 +3659,19 @@
         <v>4</v>
       </c>
       <c r="B58" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E58" s="2">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
+        <v>46140</v>
+      </c>
+      <c r="C58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" t="s">
+        <v>181</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
@@ -2199,19 +3679,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" s="2">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1</v>
+        <v>46140</v>
+      </c>
+      <c r="C59" t="s">
+        <v>182</v>
+      </c>
+      <c r="D59" t="s">
+        <v>183</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -2219,19 +3699,19 @@
         <v>4</v>
       </c>
       <c r="B60" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E60" s="2">
-        <v>2</v>
-      </c>
-      <c r="F60" s="3">
-        <v>2</v>
+        <v>46140</v>
+      </c>
+      <c r="C60" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" t="s">
+        <v>184</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
@@ -2239,18 +3719,18 @@
         <v>4</v>
       </c>
       <c r="B61" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="2">
-        <v>2</v>
-      </c>
-      <c r="F61" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C61" t="s">
+        <v>185</v>
+      </c>
+      <c r="D61" t="s">
+        <v>186</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
         <v>2</v>
       </c>
     </row>
@@ -2259,18 +3739,18 @@
         <v>4</v>
       </c>
       <c r="B62" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="2">
-        <v>2</v>
-      </c>
-      <c r="F62" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C62" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
         <v>2</v>
       </c>
     </row>
@@ -2279,18 +3759,18 @@
         <v>4</v>
       </c>
       <c r="B63" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="2">
-        <v>2</v>
-      </c>
-      <c r="F63" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C63" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" t="s">
+        <v>190</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63">
         <v>2</v>
       </c>
     </row>
@@ -2299,18 +3779,18 @@
         <v>4</v>
       </c>
       <c r="B64" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E64" s="2">
-        <v>2</v>
-      </c>
-      <c r="F64" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C64" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" t="s">
+        <v>192</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64">
         <v>2</v>
       </c>
     </row>
@@ -2319,18 +3799,18 @@
         <v>4</v>
       </c>
       <c r="B65" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65" s="2">
-        <v>2</v>
-      </c>
-      <c r="F65" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
+        <v>194</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65">
         <v>2</v>
       </c>
     </row>
@@ -2339,18 +3819,18 @@
         <v>4</v>
       </c>
       <c r="B66" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E66" s="2">
-        <v>2</v>
-      </c>
-      <c r="F66" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C66" t="s">
+        <v>195</v>
+      </c>
+      <c r="D66" t="s">
+        <v>196</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66">
         <v>2</v>
       </c>
     </row>
@@ -2359,18 +3839,18 @@
         <v>4</v>
       </c>
       <c r="B67" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E67" s="2">
-        <v>2</v>
-      </c>
-      <c r="F67" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C67" t="s">
+        <v>197</v>
+      </c>
+      <c r="D67">
+        <v>654535520</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67">
         <v>2</v>
       </c>
     </row>
@@ -2379,18 +3859,18 @@
         <v>4</v>
       </c>
       <c r="B68" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E68" s="2">
-        <v>2</v>
-      </c>
-      <c r="F68" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C68" t="s">
+        <v>198</v>
+      </c>
+      <c r="D68" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68">
         <v>2</v>
       </c>
     </row>
@@ -2399,19 +3879,19 @@
         <v>4</v>
       </c>
       <c r="B69" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E69" s="2">
-        <v>2</v>
-      </c>
-      <c r="F69" s="3">
-        <v>2</v>
+        <v>46140</v>
+      </c>
+      <c r="C69" t="s">
+        <v>200</v>
+      </c>
+      <c r="D69" t="s">
+        <v>201</v>
+      </c>
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -2419,18 +3899,18 @@
         <v>4</v>
       </c>
       <c r="B70" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E70" s="2">
-        <v>2</v>
-      </c>
-      <c r="F70" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C70" t="s">
+        <v>202</v>
+      </c>
+      <c r="D70" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70">
         <v>2</v>
       </c>
     </row>
@@ -2439,18 +3919,18 @@
         <v>4</v>
       </c>
       <c r="B71" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E71" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C71" t="s">
+        <v>204</v>
+      </c>
+      <c r="D71" t="s">
+        <v>205</v>
+      </c>
+      <c r="E71">
         <v>3</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71">
         <v>1</v>
       </c>
     </row>
@@ -2459,18 +3939,18 @@
         <v>4</v>
       </c>
       <c r="B72" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E72" s="2">
-        <v>2</v>
-      </c>
-      <c r="F72" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C72" t="s">
+        <v>206</v>
+      </c>
+      <c r="D72" t="s">
+        <v>207</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72">
         <v>2</v>
       </c>
     </row>
@@ -2479,19 +3959,19 @@
         <v>4</v>
       </c>
       <c r="B73" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E73" s="2">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3">
-        <v>1</v>
+        <v>46140</v>
+      </c>
+      <c r="C73" t="s">
+        <v>208</v>
+      </c>
+      <c r="D73" t="s">
+        <v>209</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
@@ -2499,18 +3979,18 @@
         <v>4</v>
       </c>
       <c r="B74" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E74" s="2">
-        <v>2</v>
-      </c>
-      <c r="F74" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C74" t="s">
+        <v>210</v>
+      </c>
+      <c r="D74" t="s">
+        <v>211</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74">
         <v>2</v>
       </c>
     </row>
@@ -2519,13 +3999,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="7">
-        <v>46142</v>
+        <v>46140</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>45</v>
+        <v>212</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="E75" s="2">
         <v>2</v>
@@ -2539,19 +4019,19 @@
         <v>4</v>
       </c>
       <c r="B76" s="7">
-        <v>46142</v>
+        <v>46140</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="E76" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -2559,18 +4039,5094 @@
         <v>4</v>
       </c>
       <c r="B77" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C77" s="5" t="s">
+        <v>46140</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E77" s="2">
+        <v>2</v>
+      </c>
+      <c r="F77" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>4</v>
+      </c>
+      <c r="B78" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
+      </c>
+      <c r="F78" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>4</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2</v>
+      </c>
+      <c r="F79" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>4</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E80" s="2">
+        <v>2</v>
+      </c>
+      <c r="F80" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>4</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E81" s="2">
+        <v>2</v>
+      </c>
+      <c r="F81" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>4</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E82" s="2">
+        <v>3</v>
+      </c>
+      <c r="F82" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>4</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>4</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>4</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E85" s="2">
+        <v>2</v>
+      </c>
+      <c r="F85" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>4</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E86" s="2">
+        <v>4</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>4</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E87" s="2">
+        <v>2</v>
+      </c>
+      <c r="F87" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>4</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" s="2">
+        <v>2</v>
+      </c>
+      <c r="F88" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>4</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E89" s="2">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E90" s="2">
+        <v>2</v>
+      </c>
+      <c r="F90" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>4</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E91" s="2">
+        <v>2</v>
+      </c>
+      <c r="F91" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>4</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E92" s="2">
+        <v>2</v>
+      </c>
+      <c r="F92" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>4</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E93" s="2">
+        <v>2</v>
+      </c>
+      <c r="F93" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>4</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E94" s="2">
+        <v>2</v>
+      </c>
+      <c r="F94" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E95" s="2">
+        <v>2</v>
+      </c>
+      <c r="F95" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>4</v>
+      </c>
+      <c r="B96" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E96" s="2">
+        <v>2</v>
+      </c>
+      <c r="F96" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>4</v>
+      </c>
+      <c r="B97" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E97" s="2">
+        <v>2</v>
+      </c>
+      <c r="F97" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>4</v>
+      </c>
+      <c r="B98" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E98" s="2">
+        <v>2</v>
+      </c>
+      <c r="F98" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>4</v>
+      </c>
+      <c r="B99" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E99" s="2">
+        <v>2</v>
+      </c>
+      <c r="F99" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>4</v>
+      </c>
+      <c r="B100" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E100" s="2">
+        <v>2</v>
+      </c>
+      <c r="F100" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>4</v>
+      </c>
+      <c r="B101" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E101" s="2">
+        <v>2</v>
+      </c>
+      <c r="F101" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>4</v>
+      </c>
+      <c r="B102" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E102" s="2">
+        <v>2</v>
+      </c>
+      <c r="F102" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>4</v>
+      </c>
+      <c r="B103" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E103" s="2">
+        <v>2</v>
+      </c>
+      <c r="F103" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>4</v>
+      </c>
+      <c r="B104" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E104" s="2">
+        <v>2</v>
+      </c>
+      <c r="F104" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>4</v>
+      </c>
+      <c r="B105" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E105" s="2">
+        <v>2</v>
+      </c>
+      <c r="F105" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>4</v>
+      </c>
+      <c r="B106" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E106" s="2">
+        <v>2</v>
+      </c>
+      <c r="F106" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>4</v>
+      </c>
+      <c r="B107" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E107" s="2">
+        <v>2</v>
+      </c>
+      <c r="F107" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>4</v>
+      </c>
+      <c r="B108" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E108" s="2">
+        <v>2</v>
+      </c>
+      <c r="F108" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>4</v>
+      </c>
+      <c r="B109" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E109" s="2">
+        <v>2</v>
+      </c>
+      <c r="F109" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>4</v>
+      </c>
+      <c r="B110" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E110" s="2">
+        <v>2</v>
+      </c>
+      <c r="F110" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>4</v>
+      </c>
+      <c r="B111" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E111" s="2">
+        <v>2</v>
+      </c>
+      <c r="F111" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>4</v>
+      </c>
+      <c r="B112" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E112" s="2">
+        <v>3</v>
+      </c>
+      <c r="F112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>4</v>
+      </c>
+      <c r="B113" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E113" s="2">
+        <v>4</v>
+      </c>
+      <c r="F113" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>4</v>
+      </c>
+      <c r="B114" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E114" s="2">
+        <v>2</v>
+      </c>
+      <c r="F114" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>4</v>
+      </c>
+      <c r="B115" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E115" s="2">
+        <v>2</v>
+      </c>
+      <c r="F115" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>4</v>
+      </c>
+      <c r="B116" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E116" s="2">
+        <v>2</v>
+      </c>
+      <c r="F116" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>4</v>
+      </c>
+      <c r="B117" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E117" s="2">
+        <v>3</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>4</v>
+      </c>
+      <c r="B118" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E118" s="2">
+        <v>2</v>
+      </c>
+      <c r="F118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>4</v>
+      </c>
+      <c r="B119" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E119" s="2">
+        <v>3</v>
+      </c>
+      <c r="F119" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>4</v>
+      </c>
+      <c r="B120" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E120" s="2">
+        <v>2</v>
+      </c>
+      <c r="F120" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>4</v>
+      </c>
+      <c r="B121" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E121" s="2">
+        <v>2</v>
+      </c>
+      <c r="F121" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>4</v>
+      </c>
+      <c r="B122" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E122" s="2">
+        <v>3</v>
+      </c>
+      <c r="F122" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>4</v>
+      </c>
+      <c r="B123" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E123" s="2">
+        <v>2</v>
+      </c>
+      <c r="F123" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>4</v>
+      </c>
+      <c r="B124" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E124" s="2">
+        <v>2</v>
+      </c>
+      <c r="F124" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>4</v>
+      </c>
+      <c r="B125" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E125" s="2">
+        <v>3</v>
+      </c>
+      <c r="F125" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>4</v>
+      </c>
+      <c r="B126" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E126" s="2">
+        <v>2</v>
+      </c>
+      <c r="F126" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>4</v>
+      </c>
+      <c r="B127" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E127" s="2">
+        <v>2</v>
+      </c>
+      <c r="F127" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>4</v>
+      </c>
+      <c r="B128" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E128" s="2">
+        <v>2</v>
+      </c>
+      <c r="F128" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>4</v>
+      </c>
+      <c r="B129" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E129" s="2">
+        <v>2</v>
+      </c>
+      <c r="F129" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>4</v>
+      </c>
+      <c r="B130" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E130" s="2">
+        <v>3</v>
+      </c>
+      <c r="F130" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>4</v>
+      </c>
+      <c r="B131" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E131" s="2">
+        <v>2</v>
+      </c>
+      <c r="F131" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>4</v>
+      </c>
+      <c r="B132" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E132" s="2">
+        <v>2</v>
+      </c>
+      <c r="F132" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>4</v>
+      </c>
+      <c r="B133" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E133" s="2">
+        <v>2</v>
+      </c>
+      <c r="F133" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>4</v>
+      </c>
+      <c r="B134" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E134" s="2">
+        <v>4</v>
+      </c>
+      <c r="F134" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>4</v>
+      </c>
+      <c r="B135" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E135" s="2">
+        <v>2</v>
+      </c>
+      <c r="F135" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>4</v>
+      </c>
+      <c r="B136" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E136" s="2">
+        <v>2</v>
+      </c>
+      <c r="F136" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>4</v>
+      </c>
+      <c r="B137" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E137" s="2">
+        <v>2</v>
+      </c>
+      <c r="F137" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>4</v>
+      </c>
+      <c r="B138" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E138" s="2">
+        <v>2</v>
+      </c>
+      <c r="F138" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>4</v>
+      </c>
+      <c r="B139" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E139" s="2">
+        <v>2</v>
+      </c>
+      <c r="F139" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>4</v>
+      </c>
+      <c r="B140" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E140" s="2">
+        <v>4</v>
+      </c>
+      <c r="F140" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>4</v>
+      </c>
+      <c r="B141" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E141" s="2">
+        <v>2</v>
+      </c>
+      <c r="F141" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>4</v>
+      </c>
+      <c r="B142" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E142" s="2">
+        <v>2</v>
+      </c>
+      <c r="F142" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>4</v>
+      </c>
+      <c r="B143" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E143" s="2">
+        <v>2</v>
+      </c>
+      <c r="F143" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>4</v>
+      </c>
+      <c r="B144" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E144" s="2">
+        <v>2</v>
+      </c>
+      <c r="F144" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>4</v>
+      </c>
+      <c r="B145" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E145" s="2">
+        <v>4</v>
+      </c>
+      <c r="F145" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>4</v>
+      </c>
+      <c r="B146" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E146" s="2">
+        <v>2</v>
+      </c>
+      <c r="F146" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>4</v>
+      </c>
+      <c r="B147" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E147" s="2">
+        <v>2</v>
+      </c>
+      <c r="F147" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>4</v>
+      </c>
+      <c r="B148" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E148" s="2">
+        <v>2</v>
+      </c>
+      <c r="F148" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>4</v>
+      </c>
+      <c r="B149" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E149" s="2">
+        <v>1</v>
+      </c>
+      <c r="F149" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>4</v>
+      </c>
+      <c r="B150" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E150" s="2">
+        <v>4</v>
+      </c>
+      <c r="F150" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>4</v>
+      </c>
+      <c r="B151" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E151" s="2">
+        <v>2</v>
+      </c>
+      <c r="F151" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>4</v>
+      </c>
+      <c r="B152" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E152" s="2">
+        <v>2</v>
+      </c>
+      <c r="F152" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>4</v>
+      </c>
+      <c r="B153" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E153" s="2">
+        <v>3</v>
+      </c>
+      <c r="F153" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>4</v>
+      </c>
+      <c r="B154" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E154" s="2">
+        <v>2</v>
+      </c>
+      <c r="F154" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>4</v>
+      </c>
+      <c r="B155" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E155" s="2">
+        <v>2</v>
+      </c>
+      <c r="F155" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>4</v>
+      </c>
+      <c r="B156" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E156" s="2">
+        <v>2</v>
+      </c>
+      <c r="F156" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>4</v>
+      </c>
+      <c r="B157" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E157" s="2">
+        <v>2</v>
+      </c>
+      <c r="F157" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>4</v>
+      </c>
+      <c r="B158" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E158" s="2">
+        <v>2</v>
+      </c>
+      <c r="F158" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>4</v>
+      </c>
+      <c r="B159" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E159" s="2">
+        <v>2</v>
+      </c>
+      <c r="F159" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>4</v>
+      </c>
+      <c r="B160" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E160" s="2">
+        <v>2</v>
+      </c>
+      <c r="F160" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>4</v>
+      </c>
+      <c r="B161" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E161" s="2">
+        <v>2</v>
+      </c>
+      <c r="F161" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>4</v>
+      </c>
+      <c r="B162" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E162" s="2">
+        <v>4</v>
+      </c>
+      <c r="F162" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>4</v>
+      </c>
+      <c r="B163" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E163" s="2">
+        <v>4</v>
+      </c>
+      <c r="F163" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>4</v>
+      </c>
+      <c r="B164" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E164" s="2">
+        <v>2</v>
+      </c>
+      <c r="F164" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>4</v>
+      </c>
+      <c r="B165" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E165" s="2">
+        <v>2</v>
+      </c>
+      <c r="F165" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>4</v>
+      </c>
+      <c r="B166" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E166" s="2">
+        <v>2</v>
+      </c>
+      <c r="F166" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>4</v>
+      </c>
+      <c r="B167" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E167" s="2">
+        <v>2</v>
+      </c>
+      <c r="F167" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>4</v>
+      </c>
+      <c r="B168" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E168" s="2">
+        <v>2</v>
+      </c>
+      <c r="F168" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>4</v>
+      </c>
+      <c r="B169" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E169" s="2">
+        <v>2</v>
+      </c>
+      <c r="F169" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>4</v>
+      </c>
+      <c r="B170" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E170" s="2">
+        <v>2</v>
+      </c>
+      <c r="F170" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>4</v>
+      </c>
+      <c r="B171" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E171" s="2">
+        <v>2</v>
+      </c>
+      <c r="F171" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>4</v>
+      </c>
+      <c r="B172" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E172" s="2">
+        <v>2</v>
+      </c>
+      <c r="F172" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>4</v>
+      </c>
+      <c r="B173" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E173" s="2">
+        <v>2</v>
+      </c>
+      <c r="F173" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>4</v>
+      </c>
+      <c r="B174" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E174" s="2">
+        <v>4</v>
+      </c>
+      <c r="F174" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>4</v>
+      </c>
+      <c r="B175" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E175" s="2">
+        <v>2</v>
+      </c>
+      <c r="F175" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>4</v>
+      </c>
+      <c r="B176" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E176" s="2">
+        <v>2</v>
+      </c>
+      <c r="F176" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>4</v>
+      </c>
+      <c r="B177" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E177" s="2">
+        <v>2</v>
+      </c>
+      <c r="F177" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>4</v>
+      </c>
+      <c r="B178" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E178" s="2">
+        <v>3</v>
+      </c>
+      <c r="F178" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>4</v>
+      </c>
+      <c r="B179" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E179" s="2">
+        <v>2</v>
+      </c>
+      <c r="F179" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>4</v>
+      </c>
+      <c r="B180" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E180" s="2">
+        <v>4</v>
+      </c>
+      <c r="F180" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>4</v>
+      </c>
+      <c r="B181" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E181" s="2">
+        <v>4</v>
+      </c>
+      <c r="F181" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>4</v>
+      </c>
+      <c r="B182" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E182" s="2">
+        <v>2</v>
+      </c>
+      <c r="F182" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>4</v>
+      </c>
+      <c r="B183" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E183" s="2">
+        <v>4</v>
+      </c>
+      <c r="F183" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>4</v>
+      </c>
+      <c r="B184" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E184" s="2">
+        <v>4</v>
+      </c>
+      <c r="F184" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>4</v>
+      </c>
+      <c r="B185" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E185" s="2">
+        <v>2</v>
+      </c>
+      <c r="F185" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>4</v>
+      </c>
+      <c r="B186" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E186" s="2">
+        <v>2</v>
+      </c>
+      <c r="F186" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>4</v>
+      </c>
+      <c r="B187" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E187" s="2">
+        <v>2</v>
+      </c>
+      <c r="F187" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>4</v>
+      </c>
+      <c r="B188" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E188" s="2">
+        <v>4</v>
+      </c>
+      <c r="F188" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>4</v>
+      </c>
+      <c r="B189" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E189" s="2">
+        <v>4</v>
+      </c>
+      <c r="F189" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>4</v>
+      </c>
+      <c r="B190" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E190" s="2">
+        <v>2</v>
+      </c>
+      <c r="F190" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>4</v>
+      </c>
+      <c r="B191" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E191" s="2">
+        <v>2</v>
+      </c>
+      <c r="F191" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>4</v>
+      </c>
+      <c r="B192" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E192" s="2">
+        <v>2</v>
+      </c>
+      <c r="F192" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>4</v>
+      </c>
+      <c r="B193" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E193" s="2">
+        <v>2</v>
+      </c>
+      <c r="F193" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>4</v>
+      </c>
+      <c r="B194" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E194" s="2">
+        <v>2</v>
+      </c>
+      <c r="F194" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>4</v>
+      </c>
+      <c r="B195" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E195" s="2">
+        <v>2</v>
+      </c>
+      <c r="F195" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>4</v>
+      </c>
+      <c r="B196" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E196" s="2">
+        <v>2</v>
+      </c>
+      <c r="F196" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>4</v>
+      </c>
+      <c r="B197" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E197" s="2">
+        <v>4</v>
+      </c>
+      <c r="F197" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>4</v>
+      </c>
+      <c r="B198" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E198" s="2">
+        <v>2</v>
+      </c>
+      <c r="F198" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>4</v>
+      </c>
+      <c r="B199" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E199" s="2">
+        <v>2</v>
+      </c>
+      <c r="F199" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>4</v>
+      </c>
+      <c r="B200" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E200" s="2">
+        <v>2</v>
+      </c>
+      <c r="F200" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>4</v>
+      </c>
+      <c r="B201" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E201" s="2">
+        <v>2</v>
+      </c>
+      <c r="F201" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>4</v>
+      </c>
+      <c r="B202" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E202" s="2">
+        <v>2</v>
+      </c>
+      <c r="F202" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>4</v>
+      </c>
+      <c r="B203" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E203" s="2">
+        <v>2</v>
+      </c>
+      <c r="F203" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>4</v>
+      </c>
+      <c r="B204" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E204" s="2">
+        <v>2</v>
+      </c>
+      <c r="F204" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>4</v>
+      </c>
+      <c r="B205" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E205" s="2">
+        <v>2</v>
+      </c>
+      <c r="F205" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>4</v>
+      </c>
+      <c r="B206" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E206" s="2">
+        <v>2</v>
+      </c>
+      <c r="F206" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>4</v>
+      </c>
+      <c r="B207" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E207" s="2">
+        <v>2</v>
+      </c>
+      <c r="F207" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>4</v>
+      </c>
+      <c r="B208" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E208" s="2">
+        <v>2</v>
+      </c>
+      <c r="F208" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>4</v>
+      </c>
+      <c r="B209" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E209" s="2">
+        <v>2</v>
+      </c>
+      <c r="F209" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>4</v>
+      </c>
+      <c r="B210" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E210" s="2">
+        <v>2</v>
+      </c>
+      <c r="F210" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>4</v>
+      </c>
+      <c r="B211" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E211" s="2">
+        <v>2</v>
+      </c>
+      <c r="F211" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>4</v>
+      </c>
+      <c r="B212" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E212" s="2">
+        <v>2</v>
+      </c>
+      <c r="F212" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>4</v>
+      </c>
+      <c r="B213" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E213" s="2">
+        <v>3</v>
+      </c>
+      <c r="F213" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>4</v>
+      </c>
+      <c r="B214" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E214" s="2">
+        <v>2</v>
+      </c>
+      <c r="F214" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>4</v>
+      </c>
+      <c r="B215" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E215" s="2">
+        <v>2</v>
+      </c>
+      <c r="F215" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>4</v>
+      </c>
+      <c r="B216" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E216" s="2">
+        <v>2</v>
+      </c>
+      <c r="F216" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>4</v>
+      </c>
+      <c r="B217" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E217" s="2">
+        <v>4</v>
+      </c>
+      <c r="F217" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>4</v>
+      </c>
+      <c r="B218" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E218" s="2">
+        <v>3</v>
+      </c>
+      <c r="F218" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>4</v>
+      </c>
+      <c r="B219" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E219" s="2">
+        <v>2</v>
+      </c>
+      <c r="F219" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>4</v>
+      </c>
+      <c r="B220" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E220" s="2">
+        <v>2</v>
+      </c>
+      <c r="F220" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>4</v>
+      </c>
+      <c r="B221" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E221" s="2">
+        <v>2</v>
+      </c>
+      <c r="F221" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>4</v>
+      </c>
+      <c r="B222" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E222" s="2">
+        <v>2</v>
+      </c>
+      <c r="F222" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>4</v>
+      </c>
+      <c r="B223" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E223" s="2">
+        <v>3</v>
+      </c>
+      <c r="F223" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>4</v>
+      </c>
+      <c r="B224" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E224" s="2">
+        <v>3</v>
+      </c>
+      <c r="F224" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>4</v>
+      </c>
+      <c r="B225" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E225" s="2">
+        <v>2</v>
+      </c>
+      <c r="F225" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>4</v>
+      </c>
+      <c r="B226" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E226" s="2">
+        <v>2</v>
+      </c>
+      <c r="F226" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>4</v>
+      </c>
+      <c r="B227" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E227" s="2">
+        <v>2</v>
+      </c>
+      <c r="F227" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>4</v>
+      </c>
+      <c r="B228" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E228" s="2">
+        <v>2</v>
+      </c>
+      <c r="F228" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>4</v>
+      </c>
+      <c r="B229" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E229" s="2">
+        <v>2</v>
+      </c>
+      <c r="F229" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>4</v>
+      </c>
+      <c r="B230" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E230" s="2">
+        <v>4</v>
+      </c>
+      <c r="F230" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>4</v>
+      </c>
+      <c r="B231" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E231" s="2">
+        <v>2</v>
+      </c>
+      <c r="F231" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>4</v>
+      </c>
+      <c r="B232" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E232" s="2">
+        <v>2</v>
+      </c>
+      <c r="F232" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>4</v>
+      </c>
+      <c r="B233" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E233" s="2">
+        <v>2</v>
+      </c>
+      <c r="F233" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>4</v>
+      </c>
+      <c r="B234" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E234" s="2">
+        <v>4</v>
+      </c>
+      <c r="F234" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>4</v>
+      </c>
+      <c r="B235" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E235" s="2">
+        <v>2</v>
+      </c>
+      <c r="F235" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>4</v>
+      </c>
+      <c r="B236" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E236" s="2">
+        <v>2</v>
+      </c>
+      <c r="F236" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>4</v>
+      </c>
+      <c r="B237" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E237" s="2">
+        <v>2</v>
+      </c>
+      <c r="F237" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>4</v>
+      </c>
+      <c r="B238" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E238" s="2">
+        <v>2</v>
+      </c>
+      <c r="F238" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>4</v>
+      </c>
+      <c r="B239" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E239" s="2">
+        <v>2</v>
+      </c>
+      <c r="F239" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>4</v>
+      </c>
+      <c r="B240" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E240" s="2">
+        <v>2</v>
+      </c>
+      <c r="F240" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>4</v>
+      </c>
+      <c r="B241" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E241" s="2">
+        <v>2</v>
+      </c>
+      <c r="F241" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>4</v>
+      </c>
+      <c r="B242" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E242" s="2">
+        <v>2</v>
+      </c>
+      <c r="F242" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>4</v>
+      </c>
+      <c r="B243" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E243" s="2">
+        <v>2</v>
+      </c>
+      <c r="F243" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>4</v>
+      </c>
+      <c r="B244" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E244" s="2">
+        <v>2</v>
+      </c>
+      <c r="F244" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>4</v>
+      </c>
+      <c r="B245" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E245" s="2">
+        <v>2</v>
+      </c>
+      <c r="F245" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A246">
+        <v>4</v>
+      </c>
+      <c r="B246" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E246" s="2">
+        <v>2</v>
+      </c>
+      <c r="F246" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A247">
+        <v>4</v>
+      </c>
+      <c r="B247" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E247" s="2">
+        <v>2</v>
+      </c>
+      <c r="F247" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>4</v>
+      </c>
+      <c r="B248" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E248" s="2">
+        <v>2</v>
+      </c>
+      <c r="F248" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>4</v>
+      </c>
+      <c r="B249" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E249" s="2">
+        <v>2</v>
+      </c>
+      <c r="F249" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>4</v>
+      </c>
+      <c r="B250" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E250" s="2">
+        <v>2</v>
+      </c>
+      <c r="F250" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>4</v>
+      </c>
+      <c r="B251" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E251" s="2">
+        <v>2</v>
+      </c>
+      <c r="F251" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>4</v>
+      </c>
+      <c r="B252" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E252" s="2">
+        <v>2</v>
+      </c>
+      <c r="F252" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>4</v>
+      </c>
+      <c r="B253" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E253" s="2">
+        <v>4</v>
+      </c>
+      <c r="F253" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>4</v>
+      </c>
+      <c r="B254" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E254" s="2">
+        <v>2</v>
+      </c>
+      <c r="F254" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>4</v>
+      </c>
+      <c r="B255" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E255" s="2">
+        <v>2</v>
+      </c>
+      <c r="F255" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>4</v>
+      </c>
+      <c r="B256" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E256" s="2">
+        <v>2</v>
+      </c>
+      <c r="F256" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>4</v>
+      </c>
+      <c r="B257" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E257" s="2">
+        <v>2</v>
+      </c>
+      <c r="F257" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>4</v>
+      </c>
+      <c r="B258" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E258" s="2">
+        <v>2</v>
+      </c>
+      <c r="F258" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>4</v>
+      </c>
+      <c r="B259" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E259" s="2">
+        <v>2</v>
+      </c>
+      <c r="F259" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>4</v>
+      </c>
+      <c r="B260" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E260" s="2">
+        <v>2</v>
+      </c>
+      <c r="F260" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>4</v>
+      </c>
+      <c r="B261" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E261" s="2">
+        <v>2</v>
+      </c>
+      <c r="F261" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>4</v>
+      </c>
+      <c r="B262" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E262" s="2">
+        <v>2</v>
+      </c>
+      <c r="F262" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>4</v>
+      </c>
+      <c r="B263" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E263" s="2">
+        <v>4</v>
+      </c>
+      <c r="F263" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>4</v>
+      </c>
+      <c r="B264" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E264" s="2">
+        <v>2</v>
+      </c>
+      <c r="F264" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>4</v>
+      </c>
+      <c r="B265" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E265" s="2">
+        <v>2</v>
+      </c>
+      <c r="F265" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>4</v>
+      </c>
+      <c r="B266" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E266" s="2">
+        <v>2</v>
+      </c>
+      <c r="F266" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>4</v>
+      </c>
+      <c r="B267" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E267" s="2">
+        <v>2</v>
+      </c>
+      <c r="F267" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>4</v>
+      </c>
+      <c r="B268" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E268" s="2">
+        <v>2</v>
+      </c>
+      <c r="F268" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>4</v>
+      </c>
+      <c r="B269" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E269" s="2">
+        <v>4</v>
+      </c>
+      <c r="F269" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>4</v>
+      </c>
+      <c r="B270" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E270" s="2">
+        <v>2</v>
+      </c>
+      <c r="F270" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>4</v>
+      </c>
+      <c r="B271" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E271" s="2">
+        <v>2</v>
+      </c>
+      <c r="F271" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>4</v>
+      </c>
+      <c r="B272" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E272" s="2">
+        <v>2</v>
+      </c>
+      <c r="F272" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>4</v>
+      </c>
+      <c r="B273" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E273" s="2">
+        <v>2</v>
+      </c>
+      <c r="F273" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>4</v>
+      </c>
+      <c r="B274" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E274" s="2">
+        <v>2</v>
+      </c>
+      <c r="F274" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>4</v>
+      </c>
+      <c r="B275" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E275" s="2">
+        <v>2</v>
+      </c>
+      <c r="F275" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>4</v>
+      </c>
+      <c r="B276" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E276" s="2">
+        <v>2</v>
+      </c>
+      <c r="F276" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>4</v>
+      </c>
+      <c r="B277" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E277" s="2">
+        <v>2</v>
+      </c>
+      <c r="F277" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>4</v>
+      </c>
+      <c r="B278" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E278" s="2">
+        <v>2</v>
+      </c>
+      <c r="F278" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>4</v>
+      </c>
+      <c r="B279" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E279" s="2">
+        <v>2</v>
+      </c>
+      <c r="F279" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>4</v>
+      </c>
+      <c r="B280" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E280" s="2">
+        <v>2</v>
+      </c>
+      <c r="F280" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>4</v>
+      </c>
+      <c r="B281" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E281" s="2">
+        <v>2</v>
+      </c>
+      <c r="F281" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>4</v>
+      </c>
+      <c r="B282" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E282" s="2">
+        <v>2</v>
+      </c>
+      <c r="F282" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>4</v>
+      </c>
+      <c r="B283" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E283" s="2">
+        <v>4</v>
+      </c>
+      <c r="F283" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>4</v>
+      </c>
+      <c r="B284" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E284" s="2">
+        <v>2</v>
+      </c>
+      <c r="F284" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>4</v>
+      </c>
+      <c r="B285" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E285" s="2">
+        <v>2</v>
+      </c>
+      <c r="F285" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>4</v>
+      </c>
+      <c r="B286" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E286" s="2">
+        <v>2</v>
+      </c>
+      <c r="F286" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>4</v>
+      </c>
+      <c r="B287" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E287" s="2">
+        <v>2</v>
+      </c>
+      <c r="F287" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>4</v>
+      </c>
+      <c r="B288" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E288" s="2">
+        <v>3</v>
+      </c>
+      <c r="F288" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>4</v>
+      </c>
+      <c r="B289" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E289" s="2">
+        <v>2</v>
+      </c>
+      <c r="F289" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>4</v>
+      </c>
+      <c r="B290" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E290" s="2">
+        <v>2</v>
+      </c>
+      <c r="F290" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>4</v>
+      </c>
+      <c r="B291" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E291" s="2">
+        <v>2</v>
+      </c>
+      <c r="F291" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>4</v>
+      </c>
+      <c r="B292" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D292" s="2">
+        <v>673834535</v>
+      </c>
+      <c r="E292" s="2">
+        <v>2</v>
+      </c>
+      <c r="F292" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>4</v>
+      </c>
+      <c r="B293" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E293" s="2">
+        <v>2</v>
+      </c>
+      <c r="F293" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>4</v>
+      </c>
+      <c r="B294" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E294" s="2">
+        <v>2</v>
+      </c>
+      <c r="F294" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>4</v>
+      </c>
+      <c r="B295" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E295" s="2">
+        <v>3</v>
+      </c>
+      <c r="F295" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>4</v>
+      </c>
+      <c r="B296" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D296" s="2">
+        <v>678322491</v>
+      </c>
+      <c r="E296" s="2">
+        <v>2</v>
+      </c>
+      <c r="F296" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>4</v>
+      </c>
+      <c r="B297" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E297" s="2">
+        <v>2</v>
+      </c>
+      <c r="F297" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>4</v>
+      </c>
+      <c r="B298" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E298" s="2">
+        <v>2</v>
+      </c>
+      <c r="F298" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>4</v>
+      </c>
+      <c r="B299" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E299" s="2">
+        <v>2</v>
+      </c>
+      <c r="F299" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>4</v>
+      </c>
+      <c r="B300" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E300" s="2">
+        <v>2</v>
+      </c>
+      <c r="F300" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>4</v>
+      </c>
+      <c r="B301" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C301" s="1"/>
+      <c r="D301" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E301" s="2">
+        <v>2</v>
+      </c>
+      <c r="F301" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>4</v>
+      </c>
+      <c r="B302" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E302" s="2">
+        <v>2</v>
+      </c>
+      <c r="F302" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>4</v>
+      </c>
+      <c r="B303" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E303" s="2">
+        <v>2</v>
+      </c>
+      <c r="F303" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>4</v>
+      </c>
+      <c r="B304" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E304" s="2">
+        <v>2</v>
+      </c>
+      <c r="F304" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>4</v>
+      </c>
+      <c r="B305" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E305" s="2">
+        <v>2</v>
+      </c>
+      <c r="F305" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>4</v>
+      </c>
+      <c r="B306" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C306" s="1"/>
+      <c r="D306" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E306" s="2">
+        <v>2</v>
+      </c>
+      <c r="F306" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>4</v>
+      </c>
+      <c r="B307" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E307" s="2">
+        <v>4</v>
+      </c>
+      <c r="F307" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>4</v>
+      </c>
+      <c r="B308" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E308" s="2">
+        <v>2</v>
+      </c>
+      <c r="F308" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>4</v>
+      </c>
+      <c r="B309" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E309" s="2">
+        <v>2</v>
+      </c>
+      <c r="F309" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>4</v>
+      </c>
+      <c r="B310" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E310" s="2">
+        <v>4</v>
+      </c>
+      <c r="F310" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>4</v>
+      </c>
+      <c r="B311" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E311" s="2">
+        <v>2</v>
+      </c>
+      <c r="F311" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>4</v>
+      </c>
+      <c r="B312" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E312" s="2">
+        <v>4</v>
+      </c>
+      <c r="F312" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>4</v>
+      </c>
+      <c r="B313" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E313" s="2">
+        <v>3</v>
+      </c>
+      <c r="F313" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>4</v>
+      </c>
+      <c r="B314" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E314" s="2">
+        <v>2</v>
+      </c>
+      <c r="F314" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>4</v>
+      </c>
+      <c r="B315" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E315" s="2">
+        <v>2</v>
+      </c>
+      <c r="F315" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>4</v>
+      </c>
+      <c r="B316" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E316" s="2">
+        <v>2</v>
+      </c>
+      <c r="F316" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>4</v>
+      </c>
+      <c r="B317" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E317" s="2">
+        <v>2</v>
+      </c>
+      <c r="F317" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>4</v>
+      </c>
+      <c r="B318" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E318" s="2">
+        <v>2</v>
+      </c>
+      <c r="F318" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>4</v>
+      </c>
+      <c r="B319" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E319" s="2">
+        <v>2</v>
+      </c>
+      <c r="F319" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>4</v>
+      </c>
+      <c r="B320" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E320" s="2">
+        <v>2</v>
+      </c>
+      <c r="F320" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>4</v>
+      </c>
+      <c r="B321" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E321" s="2">
+        <v>2</v>
+      </c>
+      <c r="F321" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>4</v>
+      </c>
+      <c r="B322" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E322" s="2">
+        <v>2</v>
+      </c>
+      <c r="F322" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>4</v>
+      </c>
+      <c r="B323" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E323" s="2">
+        <v>2</v>
+      </c>
+      <c r="F323" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>4</v>
+      </c>
+      <c r="B324" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E324" s="2">
+        <v>2</v>
+      </c>
+      <c r="F324" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>4</v>
+      </c>
+      <c r="B325" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E325" s="2">
+        <v>3</v>
+      </c>
+      <c r="F325" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>4</v>
+      </c>
+      <c r="B326" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E326" s="2">
+        <v>2</v>
+      </c>
+      <c r="F326" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>4</v>
+      </c>
+      <c r="B327" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E327" s="2">
+        <v>3</v>
+      </c>
+      <c r="F327" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>4</v>
+      </c>
+      <c r="B328" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E328" s="2">
+        <v>2</v>
+      </c>
+      <c r="F328" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>4</v>
+      </c>
+      <c r="B329" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E329" s="2">
+        <v>2</v>
+      </c>
+      <c r="F329" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>4</v>
+      </c>
+      <c r="B330" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E330" s="2">
+        <v>2</v>
+      </c>
+      <c r="F330" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>4</v>
+      </c>
+      <c r="B331" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C331" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D331" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E77" s="4">
-        <v>2</v>
-      </c>
-      <c r="F77" s="6">
+      <c r="E331" s="4">
+        <v>2</v>
+      </c>
+      <c r="F331" s="6">
         <v>2</v>
       </c>
     </row>
